--- a/flights.xlsx
+++ b/flights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ricca/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nmaratos/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C0C31C-4B2D-5D41-B4E2-5CBA41BAC00A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A4D9F02-12F8-D148-986D-E5F2298BAEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19660" xr2:uid="{A8A566B9-0631-5847-BCD9-EE5E8A47F86B}"/>
+    <workbookView xWindow="58580" yWindow="-8380" windowWidth="29400" windowHeight="17300" xr2:uid="{A8A566B9-0631-5847-BCD9-EE5E8A47F86B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="54">
   <si>
     <t>Airline</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t>Mar'27</t>
+  </si>
+  <si>
+    <t>May '27</t>
   </si>
 </sst>
 </file>
@@ -317,7 +320,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>203200</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -378,7 +381,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>203200</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1594,7 +1597,33 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" ht="20" x14ac:dyDescent="0.2">
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F33" s="8">
+        <v>282000</v>
+      </c>
+      <c r="G33" s="7">
+        <v>791</v>
+      </c>
+      <c r="H33" s="8">
+        <v>12445</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A38" s="14"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -1603,7 +1632,7 @@
       <c r="F38" s="14"/>
       <c r="G38" s="14"/>
     </row>
-    <row r="47" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/flights.xlsx
+++ b/flights.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nmaratos/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A4D9F02-12F8-D148-986D-E5F2298BAEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE8D03E-B809-E545-9180-9C9DDF463993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58580" yWindow="-8380" windowWidth="29400" windowHeight="17300" xr2:uid="{A8A566B9-0631-5847-BCD9-EE5E8A47F86B}"/>
+    <workbookView xWindow="14720" yWindow="680" windowWidth="14680" windowHeight="17300" xr2:uid="{A8A566B9-0631-5847-BCD9-EE5E8A47F86B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="55">
   <si>
     <t>Airline</t>
   </si>
@@ -202,6 +202,9 @@
   </si>
   <si>
     <t>May '27</t>
+  </si>
+  <si>
+    <t>Rome</t>
   </si>
 </sst>
 </file>
@@ -320,7 +323,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>203200</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -381,7 +384,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>203200</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1623,6 +1626,58 @@
         <v>12445</v>
       </c>
     </row>
+    <row r="34" spans="1:8" ht="20" x14ac:dyDescent="0.2">
+      <c r="A34" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F34" s="8">
+        <v>363000</v>
+      </c>
+      <c r="G34" s="7">
+        <v>246</v>
+      </c>
+      <c r="H34" s="8">
+        <v>12552</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="20" x14ac:dyDescent="0.2">
+      <c r="A35" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" s="8">
+        <v>363000</v>
+      </c>
+      <c r="G35" s="7">
+        <v>253</v>
+      </c>
+      <c r="H35" s="8">
+        <v>11121</v>
+      </c>
+    </row>
     <row r="38" spans="1:8" ht="18" x14ac:dyDescent="0.2">
       <c r="A38" s="14"/>
       <c r="B38" s="14"/>

--- a/flights.xlsx
+++ b/flights.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nmaratos/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nmaratos/Documents/Pay Calculator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE8D03E-B809-E545-9180-9C9DDF463993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8485F6F0-B053-084F-A1FE-8160643AF9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14720" yWindow="680" windowWidth="14680" windowHeight="17300" xr2:uid="{A8A566B9-0631-5847-BCD9-EE5E8A47F86B}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17300" xr2:uid="{A8A566B9-0631-5847-BCD9-EE5E8A47F86B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="57">
   <si>
     <t>Airline</t>
   </si>
@@ -205,6 +205,12 @@
   </si>
   <si>
     <t>Rome</t>
+  </si>
+  <si>
+    <t>Christchurch</t>
+  </si>
+  <si>
+    <t>Mar '27</t>
   </si>
 </sst>
 </file>
@@ -914,7 +920,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F6" s="4">
         <v>282000</v>
@@ -1676,6 +1682,32 @@
       </c>
       <c r="H35" s="8">
         <v>11121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="20" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="8">
+        <v>134200</v>
+      </c>
+      <c r="G36" s="7">
+        <v>243</v>
+      </c>
+      <c r="H36" s="8">
+        <v>3505</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="18" x14ac:dyDescent="0.2">
